--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T13:19:08+00:00</t>
+    <t>2025-12-23T13:30:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T13:30:37+00:00</t>
+    <t>2025-12-23T13:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T13:47:13+00:00</t>
+    <t>2025-12-23T14:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T14:00:44+00:00</t>
+    <t>2025-12-23T14:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T14:16:40+00:00</t>
+    <t>2025-12-29T12:28:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T12:28:59+00:00</t>
+    <t>2025-12-29T12:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T12:57:50+00:00</t>
+    <t>2025-12-29T13:00:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T13:00:52+00:00</t>
+    <t>2025-12-29T13:00:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T13:00:32+00:00</t>
+    <t>2025-12-29T13:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T13:15:57+00:00</t>
+    <t>2025-12-29T13:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T13:18:38+00:00</t>
+    <t>2025-12-29T13:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T13:24:54+00:00</t>
+    <t>2025-12-29T13:29:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T13:29:27+00:00</t>
+    <t>2025-12-29T13:42:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T13:42:20+00:00</t>
+    <t>2025-12-29T14:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T14:29:02+00:00</t>
+    <t>2025-12-29T14:27:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T14:27:33+00:00</t>
+    <t>2025-12-29T14:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T14:28:10+00:00</t>
+    <t>2025-12-29T14:39:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T14:39:46+00:00</t>
+    <t>2025-12-29T15:02:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T15:02:13+00:00</t>
+    <t>2025-12-29T15:10:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T15:10:06+00:00</t>
+    <t>2025-12-29T15:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T15:27:17+00:00</t>
+    <t>2025-12-29T15:39:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T15:39:17+00:00</t>
+    <t>2025-12-29T15:51:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T15:51:46+00:00</t>
+    <t>2025-12-29T16:00:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T16:00:26+00:00</t>
+    <t>2025-12-29T16:05:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T16:05:48+00:00</t>
+    <t>2026-01-09T13:44:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
+++ b/nr-update-pages/ig/ValueSet-fr-route-of-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-09T13:44:02+00:00</t>
+    <t>2026-01-16T18:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
